--- a/basedatos_partidas/salida/descompuestos/07.05.02.010.xlsx
+++ b/basedatos_partidas/salida/descompuestos/07.05.02.010.xlsx
@@ -584,10 +584,10 @@
         <v>0.24</v>
       </c>
       <c r="G11" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="12">
@@ -610,10 +610,10 @@
         <v>0.22</v>
       </c>
       <c r="G12" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="H12" t="n">
-        <v>1.58</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="13">
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>44.98</v>
+        <v>45.21</v>
       </c>
     </row>
     <row r="17">
@@ -899,7 +899,7 @@
         <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>55.06</v>
+        <v>55.29</v>
       </c>
       <c r="H27" t="n">
         <v>0.55</v>
@@ -918,7 +918,7 @@
       </c>
       <c r="G28" s="4" t="n"/>
       <c r="H28" s="5" t="n">
-        <v>55.61</v>
+        <v>55.84</v>
       </c>
     </row>
   </sheetData>
